--- a/DATA/MASTER/C10_MASTER/Resultados_EDA/Analisis_Bivariado/indice_resultados.xlsx
+++ b/DATA/MASTER/C10_MASTER/Resultados_EDA/Analisis_Bivariado/indice_resultados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Descripción</t>
+          <t>Descripcion</t>
         </is>
       </c>
     </row>
@@ -448,79 +448,175 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Matriz Pearson</t>
+          <t>Matriz de correlación Pearson</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>correlacion_spearman.csv</t>
+          <t>correlacion_pearson.xlsx</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Matriz Spearman</t>
+          <t>Matriz de correlación Pearson</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>heatmap_pearson.png</t>
+          <t>correlacion_pearson.md</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mapa de calor Pearson</t>
+          <t>Matriz de correlación Pearson</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>heatmap_spearman.png</t>
+          <t>correlacion_spearman.csv</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mapa de calor Spearman</t>
+          <t>Matriz de correlación Spearman</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ranking_correlaciones.csv</t>
+          <t>correlacion_spearman.xlsx</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ranking de correlaciones</t>
+          <t>Matriz de correlación Spearman</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>variables_redundantes.csv</t>
+          <t>correlacion_spearman.md</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Variables redundantes</t>
+          <t>Matriz de correlación Spearman</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>heatmap_pearson.png</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mapa de calor Pearson</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>heatmap_spearman.png</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mapa de calor Spearman</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ranking_correlaciones.csv</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ranking de correlaciones con soporte muestral</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ranking_correlaciones.xlsx</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ranking de correlaciones con soporte muestral</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ranking_correlaciones.md</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ranking de correlaciones con soporte muestral</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>variables_redundantes.csv</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pares con posible redundancia y n &gt;= 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>variables_redundantes.xlsx</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Pares con posible redundancia y n &gt;= 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>variables_redundantes.md</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pares con posible redundancia y n &gt;= 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Informe_Correlaciones.md</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Informe automático</t>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Informe automático de correlaciones</t>
         </is>
       </c>
     </row>
